--- a/libros_compras/Roberto Orlando Marroquin Gonzalez_1_2023_compras_mh.xlsx
+++ b/libros_compras/Roberto Orlando Marroquin Gonzalez_1_2023_compras_mh.xlsx
@@ -14,14 +14,83 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+  <si>
+    <t>Roberto Orlando Marroquin Gonzalez</t>
+  </si>
+  <si>
+    <t>Registro  293291-5</t>
+  </si>
+  <si>
+    <t>NIT  0614-220796-133-8</t>
+  </si>
+  <si>
+    <t>Libro de Compras del mes de Enero/2023</t>
+  </si>
+  <si>
+    <t>Correlativo</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Clase de Doc</t>
+  </si>
+  <si>
+    <t>Tipo de Doc</t>
+  </si>
+  <si>
+    <t>N de Doc</t>
+  </si>
+  <si>
+    <t>Nit</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Comp Loc Exen</t>
+  </si>
+  <si>
+    <t>Inter Exen</t>
+  </si>
+  <si>
+    <t>Impor Exen</t>
+  </si>
+  <si>
+    <t>Comp Loc Grav</t>
+  </si>
+  <si>
+    <t>Inter Grav Bienes</t>
+  </si>
+  <si>
+    <t>Impor Grav Bienes</t>
+  </si>
+  <si>
+    <t>Impor Grav Servicios</t>
+  </si>
+  <si>
+    <t>Crdto Fiscal</t>
+  </si>
+  <si>
+    <t>Total Compra</t>
+  </si>
+  <si>
+    <t>Retencion/Pretencion</t>
+  </si>
+  <si>
+    <t>Anticipo Cta Iva</t>
+  </si>
+  <si>
+    <t>IVA Terceros</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
   <si>
     <t>04/01/2024</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>03</t>
   </si>
   <si>
@@ -43,16 +112,24 @@
     <t>169.50</t>
   </si>
   <si>
-    <t>3</t>
+    <t>Totales</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,7 +151,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -82,13 +159,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -385,74 +480,270 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
   <pageMargins left="0.26" right="0.26" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
 </worksheet>
 </file>